--- a/naver-place-crawler/results_health/관악_헬스장.xlsx
+++ b/naver-place-crawler/results_health/관악_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V101"/>
+  <dimension ref="A1:V163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -7515,34 +7515,34 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>운동하는날 서울대봉천점</t>
+          <t>크라운짐 난곡점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>fitnessday005@naver.com</t>
+          <t>whdudgkr69@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1313-8298</t>
+          <t>0507-1324-7163</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 쑥고개로 75 광장빌딩 B1</t>
+          <t>서울특별시 관악구 미성길 27</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessday005/223687502829</t>
+          <t>https://blog.naver.com/PostList.naver?blogId=whdudgkr69</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7573,17 +7573,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>353</v>
+        <v>171</v>
       </c>
       <c r="Q76" t="n">
-        <v>788</v>
+        <v>676</v>
       </c>
       <c r="R76" t="n">
-        <v>1141</v>
+        <v>847</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7592,12 +7592,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1275339710</t>
+          <t>34016838</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1275339710</t>
+          <t>https://m.place.naver.com/place/34016838</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7609,34 +7609,34 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>그린짐 PT</t>
+          <t>힙짐PT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>onefitseoul@naver.com</t>
+          <t>wndlrhs23@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1490-2304</t>
+          <t>0507-1467-3531</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로180길 6 2층 그린짐</t>
+          <t>서울특별시 관악구 대학5길 6 2층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onefitseoul</t>
+          <t>https://open.kakao.com/o/shGx8vQe</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7662,7 +7662,7 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7671,13 +7671,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="Q77" t="n">
-        <v>552</v>
+        <v>40</v>
       </c>
       <c r="R77" t="n">
-        <v>635</v>
+        <v>78</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1901790726</t>
+          <t>1489250657</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1901790726</t>
+          <t>https://m.place.naver.com/place/1489250657</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7703,34 +7703,34 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>터틀짐</t>
+          <t>어반짐 서울대입구역점</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>turtlegym@naver.com</t>
+          <t>sweetguy_300@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1320-9685</t>
+          <t>0507-1462-7710</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 조원로 56 4층</t>
+          <t>서울특별시 관악구 남부순환로 1798 지하1층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sJsn01Uh</t>
+          <t>https://blog.naver.com/sweetguy_300</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7756,7 +7756,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7765,13 +7765,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>307</v>
+        <v>1457</v>
       </c>
       <c r="Q78" t="n">
-        <v>159</v>
+        <v>3552</v>
       </c>
       <c r="R78" t="n">
-        <v>466</v>
+        <v>5009</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1639610584</t>
+          <t>1333323901</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639610584</t>
+          <t>https://m.place.naver.com/place/1333323901</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7797,34 +7797,30 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>레시핏 낙성대점</t>
+          <t>크로스핏 타우너</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>recifit_pt@naver.com</t>
+          <t>chlcnswk43@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0507-1481-8308</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 1939 태양빌딩 2층 레시핏</t>
+          <t>서울특별시 관악구 남현1길 68-18 지하 1층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/recifit_pt</t>
+          <t>https://www.instagram.com/crossfit_towner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7839,7 +7835,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7859,13 +7855,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>352</v>
+        <v>42</v>
       </c>
       <c r="Q79" t="n">
-        <v>648</v>
+        <v>16</v>
       </c>
       <c r="R79" t="n">
-        <v>1000</v>
+        <v>58</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7874,12 +7870,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>36305263</t>
+          <t>1925280268</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36305263</t>
+          <t>https://m.place.naver.com/place/1925280268</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7891,34 +7887,34 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>유얼스짐PT 신대방역점</t>
+          <t>동방짐피트니스 신림서원역점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>yours_gym21@naver.com</t>
+          <t>dongbanggym@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1380-0238</t>
+          <t>0507-1431-1403</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 난곡로 357 202호</t>
+          <t>서울특별시 관악구 신림로 266 3층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yours_gym21</t>
+          <t>https://blog.naver.com/dongbanggym</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7949,17 +7945,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>436</v>
+        <v>149</v>
       </c>
       <c r="Q80" t="n">
-        <v>259</v>
+        <v>34</v>
       </c>
       <c r="R80" t="n">
-        <v>695</v>
+        <v>183</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7968,12 +7964,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1147253493</t>
+          <t>1382178948</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147253493</t>
+          <t>https://m.place.naver.com/place/1382178948</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7985,34 +7981,34 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>비더원PT 신대방역점</t>
+          <t>제임스짐휘트니스 청림점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>betheonept@naver.com</t>
+          <t>lsjun6629@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1307-2820</t>
+          <t>02-877-7701</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신사로 116-1 6층</t>
+          <t>서울특별시 관악구 관악로40길 47 제1동 제2층 제5호, 제6호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/betheonept</t>
+          <t>http://jamesgym.co.kr/</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8027,7 +8023,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8038,22 +8034,22 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>257</v>
+        <v>110</v>
       </c>
       <c r="Q81" t="n">
-        <v>265</v>
+        <v>13</v>
       </c>
       <c r="R81" t="n">
-        <v>522</v>
+        <v>123</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8062,12 +8058,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1813909427</t>
+          <t>197090464</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1813909427</t>
+          <t>https://m.place.naver.com/place/197090464</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8079,34 +8075,34 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>정피트니스PT 2호점</t>
+          <t>데일리휘트니스 난곡점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>junginyeol@naver.com</t>
+          <t>dailypt@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1486-6703</t>
+          <t>0507-1396-5565</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 시흥대로 568</t>
+          <t>서울특별시 관악구 난곡로 100 1층 103호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/junginyeol</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8116,20 +8112,24 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w444k8</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr">
         <is>
           <t>X</t>
@@ -8137,17 +8137,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="Q82" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="R82" t="n">
-        <v>213</v>
+        <v>337</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8156,12 +8156,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1229844603</t>
+          <t>1413620265</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229844603</t>
+          <t>https://m.place.naver.com/place/1413620265</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8173,30 +8173,34 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 신림</t>
+          <t>커브스 봉천클럽</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>goodhabit_yeonnam@naver.com</t>
+          <t>dlahrwl@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>02-877-3090</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로 391 4층</t>
+          <t>서울특별시 관악구 양녕로 58 농협 3층 301호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_yeonnam</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8206,20 +8210,24 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w84jieo</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
           <t>X</t>
@@ -8231,13 +8239,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>629</v>
+        <v>102</v>
       </c>
       <c r="Q83" t="n">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="R83" t="n">
-        <v>798</v>
+        <v>181</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8246,12 +8254,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1979699403</t>
+          <t>13299207</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979699403</t>
+          <t>https://m.place.naver.com/place/13299207</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8263,34 +8271,34 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>핏라운지PT 신림점</t>
+          <t>파운드짐 헬스&amp;PT 신림역점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>fitlounge01@naver.com</t>
+          <t>founds1@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1310-9499</t>
+          <t>0507-1442-9679</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 1630 지하1층</t>
+          <t>서울특별시 관악구 신림로 350 지하1층 파운드짐</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitlounge01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8300,20 +8308,24 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4julq</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr">
         <is>
           <t>X</t>
@@ -8325,13 +8337,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>113</v>
+        <v>3576</v>
       </c>
       <c r="Q84" t="n">
-        <v>659</v>
+        <v>692</v>
       </c>
       <c r="R84" t="n">
-        <v>772</v>
+        <v>4268</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8340,12 +8352,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1429308054</t>
+          <t>1401450856</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429308054</t>
+          <t>https://m.place.naver.com/place/1401450856</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8357,34 +8369,34 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>플렉스짐 서울대입구역점</t>
+          <t>얼티밋트레이닝 신림점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>flexgympt1@naver.com</t>
+          <t>hoitjja93@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1322-6723</t>
+          <t>02-875-2023</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 쑥고개로 121 지하1층</t>
+          <t>서울특별시 관악구 봉천로14길 12 지하1층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/flexgympt1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8394,20 +8406,24 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41mv0</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr">
         <is>
           <t>X</t>
@@ -8415,17 +8431,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>60</v>
+        <v>527</v>
       </c>
       <c r="Q85" t="n">
-        <v>303</v>
+        <v>74</v>
       </c>
       <c r="R85" t="n">
-        <v>363</v>
+        <v>601</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8434,12 +8450,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>240118000</t>
+          <t>1373634835</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/240118000</t>
+          <t>https://m.place.naver.com/place/1373634835</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8451,34 +8467,34 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>유얼스짐PT 구로디지털점</t>
+          <t>피스트엑스 서울대입구</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>yours_gym21@naver.com</t>
+          <t>fisttraining@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>02-839-0102</t>
+          <t>0507-1370-1532</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 조원로 10-1 2층</t>
+          <t>서울특별시 관악구 봉천로 456 영인MC빌딩 지하1층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yoursgym_/</t>
+          <t>https://fist-x.com</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8498,10 +8514,14 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ls36</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr">
         <is>
           <t>X</t>
@@ -8513,13 +8533,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>377</v>
+        <v>1188</v>
       </c>
       <c r="Q86" t="n">
-        <v>755</v>
+        <v>1594</v>
       </c>
       <c r="R86" t="n">
-        <v>1132</v>
+        <v>2782</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8528,12 +8548,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1434675982</t>
+          <t>1528196450</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434675982</t>
+          <t>https://m.place.naver.com/place/1528196450</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8545,34 +8565,34 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>짐플렉스 PT</t>
+          <t>스포애니 은천점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>korean_lifter@naver.com</t>
+          <t>spoany30@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1407-7862</t>
+          <t>0507-1362-9618</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로 300 웅산빌딩 2층 GYMFLEXX(짐플렉스 PT)</t>
+          <t>서울특별시 관악구 은천로 51 은호빌딩 B1층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/korean_lifter</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8582,20 +8602,24 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ilmq</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr">
         <is>
           <t>X</t>
@@ -8607,13 +8631,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>43</v>
+        <v>960</v>
       </c>
       <c r="Q87" t="n">
-        <v>10</v>
+        <v>887</v>
       </c>
       <c r="R87" t="n">
-        <v>53</v>
+        <v>1847</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8622,12 +8646,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2049531928</t>
+          <t>37009416</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049531928</t>
+          <t>https://m.place.naver.com/place/37009416</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8639,29 +8663,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>엠제이핏PT</t>
+          <t>프로틴짐헬스&amp;PT 서울대입구점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>rethug@naver.com</t>
+          <t>proteingym_seoul@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1397-3263</t>
+          <t>0507-1361-9684</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 은천로 48 2층 엠제이핏PT</t>
+          <t>서울특별시 관악구 관악로 186 지하1층 B01호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8686,10 +8710,14 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyy1ssq</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr">
         <is>
           <t>X</t>
@@ -8697,17 +8725,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="Q88" t="n">
-        <v>39</v>
+        <v>710</v>
       </c>
       <c r="R88" t="n">
-        <v>87</v>
+        <v>864</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8716,12 +8744,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1453375238</t>
+          <t>1016693454</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1453375238</t>
+          <t>https://m.place.naver.com/place/1016693454</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8733,34 +8761,34 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>유얼스짐PT 신림역점</t>
+          <t>헬스걸피트니스 낙성대점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>yoursgym3@naver.com</t>
+          <t>gonggam_fitness@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1335-3149</t>
+          <t>0507-1392-0385</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로 367 4층</t>
+          <t>서울특별시 관악구 남부순환로 1929-5 지층 1호</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yoursgym3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8770,20 +8798,24 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmcrzc6</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
           <t>X</t>
@@ -8791,17 +8823,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>262</v>
+        <v>875</v>
       </c>
       <c r="Q89" t="n">
-        <v>318</v>
+        <v>141</v>
       </c>
       <c r="R89" t="n">
-        <v>580</v>
+        <v>1016</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8810,12 +8842,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1223103296</t>
+          <t>1044862402</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223103296</t>
+          <t>https://m.place.naver.com/place/1044862402</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8827,34 +8859,34 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>라이프짐 서원역점</t>
+          <t>프리원핏 봉천점</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>hss6254@naver.com</t>
+          <t>thomasmoredk@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1335-7739</t>
+          <t>0507-1377-0764</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로 257 3층</t>
+          <t>서울특별시 관악구 봉천로29길 52 지하1층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hss6254</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8864,20 +8896,24 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ii3y</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr">
         <is>
           <t>X</t>
@@ -8885,17 +8921,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="Q90" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="R90" t="n">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8904,12 +8940,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1832973099</t>
+          <t>1928404977</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1832973099</t>
+          <t>https://m.place.naver.com/place/1928404977</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8921,38 +8957,34 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>태선생운동건강연구원 저스트바디짐</t>
+          <t>교통문화교육원 헬스클럽</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>taessam_@naver.com</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>ktwcau@gmail.com</t>
-        </is>
-      </c>
+          <t>xpf_fl@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1318-6490</t>
+          <t>02-585-3396</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 난곡로63길 30 근영빌딩 2층 3층</t>
+          <t>서울특별시 관악구 남현1길 38-10 1층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TAESSAM</t>
+          <t>http://www.stecc.or.kr/</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8987,13 +9019,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="R91" t="n">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9002,12 +9034,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1074657047</t>
+          <t>1420567830</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1074657047</t>
+          <t>https://m.place.naver.com/place/1420567830</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9019,34 +9051,34 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>핏티PT 봉천역점</t>
+          <t>이너멜 피트니스</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>fitt2024@naver.com</t>
+          <t>oenomelfitness@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1377-4282</t>
+          <t>0507-1415-9680</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 1709 3층 301호</t>
+          <t>서울특별시 관악구 호암로26길 47 지하 1층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/Fitt_seoul</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9056,7 +9088,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9066,28 +9098,32 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q195</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>62</v>
+        <v>229</v>
       </c>
       <c r="Q92" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R92" t="n">
-        <v>96</v>
+        <v>256</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9096,12 +9132,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1297962217</t>
+          <t>1149234119</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1297962217</t>
+          <t>https://m.place.naver.com/place/1149234119</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9113,44 +9149,44 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>파워존 낙성대점</t>
+          <t>휘트니스에일린 봉천점</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>powerzonechin@naver.com</t>
+          <t>yoondo211@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0507-1405-0731</t>
+          <t>0507-1314-0927</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 1899 인헌빌딩 4층</t>
+          <t>서울특별시 관악구 남부순환로 1733 정민빌딩 B1층</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://munto.page.link/dB5v</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -9160,10 +9196,14 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bp2h</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr">
         <is>
           <t>X</t>
@@ -9175,13 +9215,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1</v>
+        <v>624</v>
       </c>
       <c r="Q93" t="n">
-        <v>78</v>
+        <v>465</v>
       </c>
       <c r="R93" t="n">
-        <v>79</v>
+        <v>1089</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9190,12 +9230,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>35964746</t>
+          <t>1998357112</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35964746</t>
+          <t>https://m.place.naver.com/place/1998357112</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9207,39 +9247,43 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>힘피티</t>
+          <t>짐박스피트니스 신림본점</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>yujini5126@naver.com</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1345-1080</t>
+          <t>0507-1359-3419</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로 276 3층</t>
+          <t>서울특별시 관악구 신림로 99 B1층 (센터스퀘어 서울대점 건물)</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/himpt1080</t>
+          <t>https://gymboxx.com/onceinayear?gym=65</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9249,18 +9293,22 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9269,13 +9317,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>63</v>
+        <v>834</v>
       </c>
       <c r="Q94" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="R94" t="n">
-        <v>143</v>
+        <v>870</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9284,12 +9332,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1382724715</t>
+          <t>1442881321</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382724715</t>
+          <t>https://m.place.naver.com/place/1442881321</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9301,34 +9349,34 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>설핏PT 신대방역점</t>
+          <t>짐스타 낙성대</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ptimmida@naver.com</t>
+          <t>gymstarfitness@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1448-1613</t>
+          <t>0507-1408-9679</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 난곡로65길 9 지하1층</t>
+          <t>서울특별시 관악구 남부순환로 1926 경동제약빌딩 지하2층</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ptimmida</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9338,20 +9386,24 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4k1rp</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr">
         <is>
           <t>X</t>
@@ -9363,13 +9415,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>124</v>
+        <v>2327</v>
       </c>
       <c r="Q95" t="n">
-        <v>178</v>
+        <v>538</v>
       </c>
       <c r="R95" t="n">
-        <v>302</v>
+        <v>2865</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9378,12 +9430,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1800303715</t>
+          <t>36428472</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1800303715</t>
+          <t>https://m.place.naver.com/place/36428472</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9395,34 +9447,34 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>근육터짐 지방빠짐</t>
+          <t>럭키 헬스클럽</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ejo3oej@naver.com</t>
+          <t>conditionf1@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1435-0411</t>
+          <t>02-885-0052</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 2062 장수약국건물 3층</t>
+          <t>서울특별시 관악구 신림로 272 대원빌딩 4층</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ejo3oej</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9432,12 +9484,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9453,17 +9505,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="Q96" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="R96" t="n">
-        <v>238</v>
+        <v>57</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9472,12 +9524,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>506955709</t>
+          <t>20277662</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/506955709</t>
+          <t>https://m.place.naver.com/place/20277662</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9489,44 +9541,40 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>온핸드짐 PT 봉천역점</t>
+          <t>에프에스짐</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>onhandgym@naver.com</t>
+          <t>jwl900711@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>0507-1313-5043</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 쑥고개로 52 2층 온핸드짐 PT</t>
+          <t>서울특별시 관악구 난곡로 227-1 3층</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://on-hand-gym.com</t>
+          <t>https://blog.naver.com/jwl900711</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9542,22 +9590,22 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="Q97" t="n">
-        <v>166</v>
+        <v>14</v>
       </c>
       <c r="R97" t="n">
-        <v>278</v>
+        <v>57</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9566,12 +9614,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1672575745</t>
+          <t>1500710484</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672575745</t>
+          <t>https://m.place.naver.com/place/1500710484</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9583,29 +9631,29 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>운동해야짐</t>
+          <t>오버탑휘트니스 헬스 PT &amp; 골프 필라테스 관악봉천점</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>undong_gym@naver.com</t>
+          <t>overtop6@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1346-9680</t>
+          <t>0507-1388-3208</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 양녕로 50 3층</t>
+          <t>서울특별시 관악구 성현로 80 301호</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9635,7 +9683,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41e4a</t>
+          <t>https://talk.naver.com/ct/w5zz2h</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -9645,17 +9693,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>302</v>
+        <v>145</v>
       </c>
       <c r="Q98" t="n">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="R98" t="n">
-        <v>397</v>
+        <v>176</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9664,12 +9712,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1436058076</t>
+          <t>1085686861</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1436058076</t>
+          <t>https://m.place.naver.com/place/1085686861</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9681,49 +9729,53 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>채육관</t>
+          <t>짐박스피트니스 봉천현대시장점</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ganghaegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1337-1342</t>
+          <t>0507-1370-6406</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로246라길 3 지하 1층</t>
+          <t>서울특별시 관악구 양녕로 46 메카플러스 7층</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymboxx.com/onceinayear?gym=50</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9733,12 +9785,12 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfn3k</t>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -9747,13 +9799,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>36</v>
+        <v>1598</v>
       </c>
       <c r="Q99" t="n">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="R99" t="n">
-        <v>173</v>
+        <v>1656</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9762,12 +9814,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1076139273</t>
+          <t>1947420161</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1076139273</t>
+          <t>https://m.place.naver.com/place/1947420161</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9779,34 +9831,34 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>실내골프연습장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GDR아카데미 투엑스휘트니스 봉천점</t>
+          <t>이도피트니스 봉천점</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2xbc9811@naver.com</t>
+          <t>2dofit@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1314-9811</t>
+          <t>0507-1368-6051</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 청림6길 3 관악 푸르지오상가 4F</t>
+          <t>서울특별시 관악구 양녕로 29 7층</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/2xbc9811</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9816,20 +9868,24 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wf7d4mk</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
           <t>X</t>
@@ -9837,17 +9893,17 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>612</v>
+        <v>342</v>
       </c>
       <c r="Q100" t="n">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="R100" t="n">
-        <v>799</v>
+        <v>488</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9856,12 +9912,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>38478577</t>
+          <t>1511488872</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38478577</t>
+          <t>https://m.place.naver.com/place/1511488872</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9873,92 +9929,6028 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>더플로우 요가 신림</t>
+          <t>바운드짐 신림역점</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>skgm1116@naver.com</t>
+          <t>boundgym_@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1313-9758</t>
+          <t>0507-1358-0834</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
+          <t>서울특별시 관악구 신림로58길 13 201호</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/boundgym05</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dpwo</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>1925</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>4082</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6007</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>1052055103</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1052055103</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>비비안 휘트니스 &amp; 필라테스 서울대입구점</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>bibian7677@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1326-7677</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1799 2층</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcltsyu</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>38</v>
+      </c>
+      <c r="R102" t="n">
+        <v>114</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>2080124773</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2080124773</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>휘트니스 에일린 낙성대점</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>choyoungdo12@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1430-0935</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1940 B1층 휘트니스 에일린 낙성대점</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pkke</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>818</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>465</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1283</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>1273286981</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1273286981</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>바디짐</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>bodygym4356@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로 84 지층</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43p8b</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>19</v>
+      </c>
+      <c r="R104" t="n">
+        <v>49</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>1183772752</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1183772752</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>무브라이프짐 난곡점</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>movelifegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0507-1420-0163</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로 194 4층</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iunv</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>435</v>
+      </c>
+      <c r="R105" t="n">
+        <v>505</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>1157653085</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1157653085</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>서울대학교 더블에스 휘트니스</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>doubless_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0507-1381-9235</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로 1 관악학생생활관 900동 B2</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsk7cmw</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>67</v>
+      </c>
+      <c r="R106" t="n">
+        <v>130</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>19551094</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19551094</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>스포애니 낙성대점</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>spoany16s@naver.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0507-1337-3451</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 인헌6길 15 3층, 4층</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zzwy</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>918</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1164</v>
+      </c>
+      <c r="R107" t="n">
+        <v>2082</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>33534975</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33534975</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>레코브 PT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0507-1479-0288</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림동길 10 3층, 레코브</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rfzm</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>18</v>
+      </c>
+      <c r="R108" t="n">
+        <v>157</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>1116616394</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1116616394</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 난곡점</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0507-1337-6460</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로 210 6,7층</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=30</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>2404</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>247</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2651</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>1992995991</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1992995991</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 신림3호점</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0507-1318-6459</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로23길 16 1층 짐박스피트니스</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=32</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>1216</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>80</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1296</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>1282157591</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282157591</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>프리원핏 서울대점</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>kdfjgklgjl@naver.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0507-1403-9795</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 쑥고개로21길 9 B1F</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/10/bizes/1171028</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>4</v>
+      </c>
+      <c r="R111" t="n">
+        <v>61</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>1831631675</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1831631675</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>유앤아이짐 헬스&amp;PT 신림역점</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>youni_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1375-9990</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로64길 9 3층</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hrwy</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>645</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>2092</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2737</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>1359477400</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359477400</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>더 슈트</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>vip1352@naver.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>02-883-5735</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로15길 3 3-5층</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>17</v>
+      </c>
+      <c r="R113" t="n">
+        <v>83</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>1233305373</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1233305373</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>운동하는날 서울대봉천점</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>fitnessday005@naver.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0507-1313-8298</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 쑥고개로 75 광장빌딩 B1</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessday005/223687502829</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>788</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1141</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>1275339710</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1275339710</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>그린짐 PT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>onefitseoul@naver.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0507-1490-2304</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로180길 6 2층 그린짐</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/onefitseoul</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>552</v>
+      </c>
+      <c r="R115" t="n">
+        <v>635</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>1901790726</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1901790726</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>터틀짐</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>turtlegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0507-1320-9685</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 조원로 56 4층</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sJsn01Uh</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>159</v>
+      </c>
+      <c r="R116" t="n">
+        <v>466</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>1639610584</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639610584</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>레시핏 낙성대점</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>recifit_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0507-1481-8308</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1939 태양빌딩 2층 레시핏</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/recifit_pt</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>352</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>648</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>36305263</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36305263</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>유얼스짐PT 신대방역점</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>yours_gym21@naver.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0507-1380-0238</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로 357 202호</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yours_gym21</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>259</v>
+      </c>
+      <c r="R118" t="n">
+        <v>695</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>1147253493</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1147253493</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>비더원PT 신대방역점</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>betheonept@naver.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0507-1307-2820</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신사로 116-1 6층</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/betheonept</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>265</v>
+      </c>
+      <c r="R119" t="n">
+        <v>522</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>1813909427</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1813909427</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>정피트니스PT 2호점</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>junginyeol@naver.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0507-1486-6703</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 시흥대로 568</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/junginyeol</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>33</v>
+      </c>
+      <c r="R120" t="n">
+        <v>213</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>1229844603</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1229844603</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 신림</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>goodhabit_yeonnam@naver.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 391 4층</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodhabit_yeonnam</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>629</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>169</v>
+      </c>
+      <c r="R121" t="n">
+        <v>798</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>1979699403</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1979699403</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>핏라운지PT 신림점</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>fitlounge01@naver.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0507-1310-9499</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1630 지하1층</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitlounge01</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>659</v>
+      </c>
+      <c r="R122" t="n">
+        <v>772</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>1429308054</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1429308054</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>플렉스짐 서울대입구역점</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>flexgympt1@naver.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>0507-1322-6723</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 쑥고개로 121 지하1층</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/flexgympt1</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>303</v>
+      </c>
+      <c r="R123" t="n">
+        <v>363</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>240118000</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/240118000</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>유얼스짐PT 구로디지털점</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>yours_gym21@naver.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>02-839-0102</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 조원로 10-1 2층</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yoursgym_/</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>377</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>755</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1132</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>1434675982</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1434675982</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>짐플렉스 PT</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>korean_lifter@naver.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>0507-1407-7862</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 300 웅산빌딩 2층 GYMFLEXX(짐플렉스 PT)</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/korean_lifter</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>10</v>
+      </c>
+      <c r="R125" t="n">
+        <v>53</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>2049531928</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2049531928</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>엠제이핏PT</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>rethug@naver.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>0507-1397-3263</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 은천로 48 2층 엠제이핏PT</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>39</v>
+      </c>
+      <c r="R126" t="n">
+        <v>87</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>1453375238</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1453375238</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>유얼스짐PT 신림역점</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>yoursgym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>0507-1335-3149</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 367 4층</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yoursgym3</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>318</v>
+      </c>
+      <c r="R127" t="n">
+        <v>580</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>1223103296</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1223103296</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>라이프짐 서원역점</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>hss6254@naver.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0507-1335-7739</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 257 3층</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hss6254</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>58</v>
+      </c>
+      <c r="R128" t="n">
+        <v>91</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>1832973099</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1832973099</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>태선생운동건강연구원 저스트바디짐</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>taessam_@naver.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ktwcau@gmail.com</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0507-1318-6490</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로63길 30 근영빌딩 2층 3층</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@TAESSAM</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>69</v>
+      </c>
+      <c r="R129" t="n">
+        <v>92</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>1074657047</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1074657047</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>핏티PT 봉천역점</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>fitt2024@naver.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0507-1377-4282</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1709 3층 301호</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/Fitt_seoul</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>34</v>
+      </c>
+      <c r="R130" t="n">
+        <v>96</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>1297962217</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1297962217</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>파워존 낙성대점</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>powerzonechin@naver.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0507-1405-0731</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1899 인헌빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://munto.page.link/dB5v</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>78</v>
+      </c>
+      <c r="R131" t="n">
+        <v>79</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>35964746</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35964746</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>힘피티</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>yujini5126@naver.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0507-1345-1080</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 276 3층</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/himpt1080</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>80</v>
+      </c>
+      <c r="R132" t="n">
+        <v>143</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>1382724715</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1382724715</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>설핏PT 신대방역점</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ptimmida@naver.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0507-1448-1613</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로65길 9 지하1층</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ptimmida</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>178</v>
+      </c>
+      <c r="R133" t="n">
+        <v>302</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>1800303715</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1800303715</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>근육터짐 지방빠짐</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ejo3oej@naver.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0507-1435-0411</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 2062 장수약국건물 3층</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ejo3oej</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>69</v>
+      </c>
+      <c r="R134" t="n">
+        <v>238</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>506955709</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/506955709</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>온핸드짐 PT 봉천역점</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>onhandgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0507-1313-5043</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 쑥고개로 52 2층 온핸드짐 PT</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://on-hand-gym.com</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>166</v>
+      </c>
+      <c r="R135" t="n">
+        <v>278</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>1672575745</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1672575745</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>운동해야짐</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>undong_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0507-1346-9680</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 양녕로 50 3층</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41e4a</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>95</v>
+      </c>
+      <c r="R136" t="n">
+        <v>397</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>1436058076</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1436058076</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>채육관</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ganghaegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>0507-1337-1342</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로246라길 3 지하 1층</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfn3k</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>137</v>
+      </c>
+      <c r="R137" t="n">
+        <v>173</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>1076139273</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1076139273</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>헤게모니짐PT 서울대입구점</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>hegemonygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0507-1350-0432</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로17길 25 B1층 101호</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hegemonygym</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>830</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1107</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>1970624685</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1970624685</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>제임스킬짐PT 서울대입구점</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>wan4545@naver.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0507-1303-9645</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로 163 3층</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/jameskill</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>1623</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2524</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>37207749</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37207749</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>릿업핏PT 보라매점</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>litupfitpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 보라매로 22 4층 릿업핏PT 보라매점</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/litupfitpt</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>166</v>
+      </c>
+      <c r="R140" t="n">
+        <v>273</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>1856324575</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1856324575</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>메루치양식장 관악점</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>dygym_anchovy-gwanak@naver.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0507-1415-0938</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1931 지하 2층</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dygym_anchovy-gwanak</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>185</v>
+      </c>
+      <c r="R141" t="n">
+        <v>294</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>1826089733</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1826089733</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>웨슬리짐PT</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>wesleygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0507-1406-5046</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 봉천로 516 4층 웨슬리짐</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wesleygym</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>237</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>427</v>
+      </c>
+      <c r="R142" t="n">
+        <v>664</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>638468825</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/638468825</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>근육형제 사당역1호점</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>allinsighter@naver.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0507-1302-7080</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 과천대로 939 지상4층</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_muscle_brothers</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>56</v>
+      </c>
+      <c r="R143" t="n">
+        <v>203</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>55725165</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/55725165</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>파인필드</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>gomom75@naver.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0507-1459-6684</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 봉천로 217-1 4층</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>6</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>1494361556</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1494361556</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>리메이크바디샵 낙성대 본점</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>chance7665@naver.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0507-1387-7665</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1888 지하1층 2호</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4drwa</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>570</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>733</v>
+      </c>
+      <c r="R145" t="n">
+        <v>1303</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>116799071</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/116799071</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>바디가드짐</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>kctown84@naver.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>070-7721-1456</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 368 화창빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cn70</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>23</v>
+      </c>
+      <c r="R146" t="n">
+        <v>90</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>1729875513</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1729875513</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>운동하는날 낙성대점</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>fitnessday11@naver.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0507-1331-7281</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 봉천로 604 진원빌딩 B1</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfn7nav</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>538</v>
+      </c>
+      <c r="R147" t="n">
+        <v>742</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>1593433524</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1593433524</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>정피트니스PT 구디1호점</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>junginyeol@naver.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>02-858-6703</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 시흥대로 548 2층</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc6964</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>196</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>268</v>
+      </c>
+      <c r="R148" t="n">
+        <v>464</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>1136754722</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136754722</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>코어핏</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>dltmddnjsdl@naver.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0507-1435-8829</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로218길 27 관전 g타워 301호</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sanx</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>100</v>
+      </c>
+      <c r="R149" t="n">
+        <v>143</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>1854872595</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1854872595</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>포인티PT 서울대입구 본점</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>pointpt_@naver.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>teddy@piehealthcare.kr</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0507-1485-0371</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1808 4층 포인티PT 서울대입구 본점</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.pointpt.training/</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ef8k</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>1295</v>
+      </c>
+      <c r="R150" t="n">
+        <v>1473</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>1707961869</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1707961869</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>휴코어PT 낙성대점</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>gyj1346@naver.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0507-1330-4099</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1944 지하1층 B01호 휴코어</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wczq0jm</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>587</v>
+      </c>
+      <c r="R151" t="n">
+        <v>637</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>1480045182</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1480045182</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>더스테이짐 신대방역점</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>thestaygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0507-1314-6185</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신사로 104-1 중앙빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thestaygym</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>100</v>
+      </c>
+      <c r="R152" t="n">
+        <v>234</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>1987052869</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1987052869</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>여성전용PT 폴인핏 신림역점</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>sillimpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0507-1434-1561</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로67길 9 3층</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fall_in_fit_</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>1134</v>
+      </c>
+      <c r="R153" t="n">
+        <v>1451</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>1762308656</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1762308656</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PT나인 신림역점</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ptnine@naver.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0507-1428-2885</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신원로 38 청암빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>http://ptnine.co.kr/</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc26iq</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>67</v>
+      </c>
+      <c r="R154" t="n">
+        <v>119</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>19801597</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19801597</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>밸런스 메이트 PT STUDIO</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>magoidioma@naver.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0507-1334-9675</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 대학길 6 3층</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@balancemate</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>81</v>
+      </c>
+      <c r="R155" t="n">
+        <v>330</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>1334951029</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1334951029</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>바디클래스 PT&amp;필라테스 신림보라매점</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>bodyclass_sinlim@naver.com</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>0507-1360-9684</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 봉천로 212 희성빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hnzf</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>371</v>
+      </c>
+      <c r="R156" t="n">
+        <v>444</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>1770155513</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1770155513</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>JS GYM</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>js-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0507-1463-2254</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로15길 6 3층 JS GYM</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zpzr</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>87</v>
+      </c>
+      <c r="R157" t="n">
+        <v>104</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>38415353</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38415353</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>바디케이PT 난곡점</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>qotjdwns0913@naver.com</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0507-1390-3383</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로 173 2층</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>23</v>
+      </c>
+      <c r="R158" t="n">
+        <v>70</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>1551883149</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1551883149</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>프로틴짐PT 서울대입구점</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>proteingym_seoul@naver.com</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0507-1415-9682</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5upc0</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>314</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>519</v>
+      </c>
+      <c r="R159" t="n">
+        <v>833</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>1401058700</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1401058700</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>천샘PT 본점</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>cheonsampt@naver.com</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0507-1416-8080</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 장군봉1길 49 2층, 3층</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e55v</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>322</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>337</v>
+      </c>
+      <c r="R160" t="n">
+        <v>659</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>37870831</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37870831</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>실내골프연습장</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>GDR아카데미 투엑스휘트니스 봉천점</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2xbc9811@naver.com</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0507-1314-9811</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 청림6길 3 관악 푸르지오상가 4F</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/2xbc9811</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>612</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>187</v>
+      </c>
+      <c r="R161" t="n">
+        <v>799</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>38478577</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38478577</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>요가원</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>더플로우 요가 신림</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>skgm1116@naver.com</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0507-1313-9758</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
           <t>서울특별시 관악구 신림로65길 24 4, 5층 더플로우</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>https://더플로우.com</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P101" t="n">
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
         <v>136</v>
       </c>
-      <c r="Q101" t="n">
+      <c r="Q162" t="n">
         <v>47</v>
       </c>
-      <c r="R101" t="n">
+      <c r="R162" t="n">
         <v>183</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr">
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
         <is>
           <t>1643360786</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="U162" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1643360786</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr">
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>찜질방</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>삼모스포렉스</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>sammosp@naver.com</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>02-871-9182</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로59길 23 지하1층</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wca0ye</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>425</v>
+      </c>
+      <c r="R163" t="n">
+        <v>858</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>1040983025</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040983025</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
